--- a/files/PRASAD_INDEX_FILE.xlsx
+++ b/files/PRASAD_INDEX_FILE.xlsx
@@ -1,15 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="164011"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30218"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\2002\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/96de1385240e287f/"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="4" documentId="8_{9EEF6021-BD9E-46A9-9146-D64EF262E914}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{73CCAED0-8C8F-4714-BBB7-7FBB4CFDBB01}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="6795"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -24,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="61" uniqueCount="46">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="64" uniqueCount="48">
   <si>
     <t>Sheet1</t>
   </si>
@@ -162,12 +163,18 @@
   </si>
   <si>
     <t>Trends in Public Issues (IPO vs FPO vs Rights)</t>
+  </si>
+  <si>
+    <t>Security-wise Price Volume Data</t>
+  </si>
+  <si>
+    <t>Sheet20</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -503,16 +510,16 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:D24"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="24.85546875" customWidth="1"/>
-    <col min="2" max="2" width="46.5703125" customWidth="1"/>
-    <col min="3" max="3" width="11.140625" customWidth="1"/>
+    <col min="1" max="1" width="24.81640625" customWidth="1"/>
+    <col min="2" max="2" width="46.54296875" customWidth="1"/>
+    <col min="3" max="3" width="11.1796875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>34</v>
       </c>
@@ -526,7 +533,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A2" s="1" t="s">
         <v>38</v>
       </c>
@@ -540,7 +547,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="1" t="s">
         <v>38</v>
       </c>
@@ -554,7 +561,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="1" t="s">
         <v>38</v>
       </c>
@@ -568,7 +575,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="1" t="s">
         <v>38</v>
       </c>
@@ -582,7 +589,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A6" s="1" t="s">
         <v>38</v>
       </c>
@@ -596,7 +603,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A7" s="1" t="s">
         <v>36</v>
       </c>
@@ -610,7 +617,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="1" t="s">
         <v>36</v>
       </c>
@@ -624,7 +631,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="1" t="s">
         <v>37</v>
       </c>
@@ -638,7 +645,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A10" s="1" t="s">
         <v>37</v>
       </c>
@@ -652,7 +659,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -666,7 +673,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="1" t="s">
         <v>37</v>
       </c>
@@ -680,7 +687,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="1" t="s">
         <v>37</v>
       </c>
@@ -694,7 +701,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A14" s="1" t="s">
         <v>37</v>
       </c>
@@ -708,7 +715,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="1" t="s">
         <v>35</v>
       </c>
@@ -722,7 +729,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="1" t="s">
         <v>35</v>
       </c>
@@ -736,7 +743,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="1" t="s">
         <v>35</v>
       </c>
@@ -750,7 +757,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A18" s="1" t="s">
         <v>35</v>
       </c>
@@ -764,7 +771,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="1" t="s">
         <v>35</v>
       </c>
@@ -778,7 +785,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="1" t="s">
         <v>35</v>
       </c>
@@ -792,20 +799,31 @@
         <v>8</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-    </row>
-    <row r="22" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="B21" t="s">
+        <v>46</v>
+      </c>
+      <c r="C21" t="s">
+        <v>47</v>
+      </c>
+      <c r="D21">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="22" spans="1:4" ht="17.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A22" s="1"/>
     </row>
-    <row r="23" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A23" s="1"/>
     </row>
-    <row r="24" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A24" s="1"/>
     </row>
   </sheetData>
-  <sortState ref="A2:D20">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:D20">
     <sortCondition descending="1" ref="A2"/>
   </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
